--- a/test_data/fixtures/ap/ap_pub.xlsx
+++ b/test_data/fixtures/ap/ap_pub.xlsx
@@ -26,7 +26,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -36,6 +36,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
       </patternFill>
     </fill>
   </fills>
@@ -51,9 +56,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -419,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I12"/>
+  <dimension ref="A1:I15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -762,6 +768,87 @@
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr"/>
     </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>AP_DIFF_YELLOW</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Changed</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" s="1" t="inlineStr">
+        <is>
+          <t>w</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>AP_DIFF_GREEN</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Changed</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>w</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>AP_DIFF_WHITE</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Changed</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>w</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
